--- a/analog/Mõõtmised.xlsx
+++ b/analog/Mõõtmised.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livettu-my.sharepoint.com/personal/karlde_taltech_ee/Documents/3/projekt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\projects\skeemitehnika-projekt-2025\analog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{6946633C-A076-4AAF-99F2-0F323CBFD6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8772DAB5-A76A-4592-8A02-4E10F0282861}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39821325-9BD9-4113-B365-3477BB2BCE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C378A2B3-E602-4683-97D9-B42B95502A72}"/>
+    <workbookView xWindow="-35415" yWindow="1245" windowWidth="17025" windowHeight="11295" xr2:uid="{C378A2B3-E602-4683-97D9-B42B95502A72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>skem</t>
   </si>
@@ -53,9 +53,6 @@
     <t>dist3</t>
   </si>
   <si>
-    <t>3.16V</t>
-  </si>
-  <si>
     <t>3.27V</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t>75.7mV</t>
   </si>
   <si>
-    <t>1.61V</t>
-  </si>
-  <si>
     <t>72.6mV</t>
   </si>
   <si>
@@ -147,13 +141,31 @@
   </si>
   <si>
     <t>7.23mA</t>
+  </si>
+  <si>
+    <t>0.563 mV</t>
+  </si>
+  <si>
+    <t>10.05 mV</t>
+  </si>
+  <si>
+    <t>35.8 mV</t>
+  </si>
+  <si>
+    <t>0.0921 mA</t>
+  </si>
+  <si>
+    <t>0.0923 mA</t>
+  </si>
+  <si>
+    <t>0.0706 mA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,10 +278,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -589,13 +597,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3D091D-7310-4A8C-814F-D016A8CE1AE2}">
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
@@ -606,75 +614,75 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="I1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="2" spans="1:18" ht="15">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1">
         <v>220</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L2" s="1">
         <v>220</v>
@@ -689,45 +697,45 @@
         <v>220</v>
       </c>
       <c r="P2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1.61</v>
+      </c>
+      <c r="D3">
+        <v>3.16</v>
       </c>
       <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
         <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" t="s">
-        <v>36</v>
       </c>
       <c r="I3" s="1">
         <v>220</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L3" s="1">
         <v>220</v>
@@ -742,13 +750,33 @@
         <v>220</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>29</v>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -760,6 +788,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="08ba64f2-343f-4c5c-95c4-82115ee1b8db" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010005A166640C2EA842BCCB49D73418B8AA" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fccf97806939c8d7ed18617c0a7e9815">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="08ba64f2-343f-4c5c-95c4-82115ee1b8db" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="262e21e52604a79dfd0e7856c417075f" ns3:_="">
     <xsd:import namespace="08ba64f2-343f-4c5c-95c4-82115ee1b8db"/>
@@ -941,14 +977,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="08ba64f2-343f-4c5c-95c4-82115ee1b8db" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -959,6 +987,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C48D2D1-4109-4657-95F2-96A09D42C463}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="08ba64f2-343f-4c5c-95c4-82115ee1b8db"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77CED24A-EF4B-4485-AEB0-3E2067D43F23}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -976,22 +1020,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C48D2D1-4109-4657-95F2-96A09D42C463}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="08ba64f2-343f-4c5c-95c4-82115ee1b8db"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2454A480-6929-4528-B429-EF74635CE431}">
   <ds:schemaRefs>

--- a/analog/Mõõtmised.xlsx
+++ b/analog/Mõõtmised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\projects\skeemitehnika-projekt-2025\analog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39821325-9BD9-4113-B365-3477BB2BCE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DA35D2-AC8E-493B-A8F0-B302A0A37DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-35415" yWindow="1245" windowWidth="17025" windowHeight="11295" xr2:uid="{C378A2B3-E602-4683-97D9-B42B95502A72}"/>
   </bookViews>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
-  <si>
-    <t>skem</t>
-  </si>
-  <si>
-    <t>real</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>dist1</t>
   </si>
@@ -159,6 +153,21 @@
   </si>
   <si>
     <t>0.0706 mA</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>1.61V</t>
+  </si>
+  <si>
+    <t>3.16V</t>
+  </si>
+  <si>
+    <t>skeem</t>
+  </si>
+  <si>
+    <t>mõõdetud</t>
   </si>
 </sst>
 </file>
@@ -208,12 +217,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -241,8 +259,8 @@
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>84618</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>531560</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>123177</xdr:rowOff>
     </xdr:to>
@@ -600,89 +618,92 @@
   <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="I1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="I2" s="1">
         <v>220</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1">
         <v>220</v>
@@ -697,45 +718,45 @@
         <v>220</v>
       </c>
       <c r="P2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1.61</v>
-      </c>
-      <c r="D3">
-        <v>3.16</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="A3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
       </c>
       <c r="I3" s="1">
         <v>220</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L3" s="1">
         <v>220</v>
@@ -750,33 +771,36 @@
         <v>220</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" t="s">
         <v>25</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>26</v>
-      </c>
-      <c r="R3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -796,6 +820,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010005A166640C2EA842BCCB49D73418B8AA" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fccf97806939c8d7ed18617c0a7e9815">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="08ba64f2-343f-4c5c-95c4-82115ee1b8db" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="262e21e52604a79dfd0e7856c417075f" ns3:_="">
     <xsd:import namespace="08ba64f2-343f-4c5c-95c4-82115ee1b8db"/>
@@ -977,15 +1010,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C48D2D1-4109-4657-95F2-96A09D42C463}">
   <ds:schemaRefs>
@@ -1003,6 +1027,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2454A480-6929-4528-B429-EF74635CE431}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77CED24A-EF4B-4485-AEB0-3E2067D43F23}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1018,12 +1050,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2454A480-6929-4528-B429-EF74635CE431}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>